--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710723</v>
+        <v>121710780</v>
       </c>
       <c r="B2" t="n">
-        <v>80573</v>
+        <v>96380</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347973</v>
+        <v>347966</v>
       </c>
       <c r="R2" t="n">
-        <v>6396614</v>
+        <v>6396622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
+        <v>80573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R3" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710723</v>
+        <v>121710606</v>
       </c>
       <c r="B3" t="n">
         <v>80573</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347973</v>
+        <v>348019</v>
       </c>
       <c r="R3" t="n">
-        <v>6396614</v>
+        <v>6396625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710606</v>
+        <v>121710723</v>
       </c>
       <c r="B4" t="n">
         <v>80573</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348019</v>
+        <v>347973</v>
       </c>
       <c r="R4" t="n">
-        <v>6396625</v>
+        <v>6396614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B2" t="n">
-        <v>96380</v>
+        <v>80573</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R2" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710723</v>
+        <v>121710780</v>
       </c>
       <c r="B4" t="n">
-        <v>80573</v>
+        <v>96380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347973</v>
+        <v>347966</v>
       </c>
       <c r="R4" t="n">
-        <v>6396614</v>
+        <v>6396622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710723</v>
+        <v>121710606</v>
       </c>
       <c r="B2" t="n">
         <v>80573</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347973</v>
+        <v>348019</v>
       </c>
       <c r="R2" t="n">
-        <v>6396614</v>
+        <v>6396625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710606</v>
+        <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>80573</v>
+        <v>96380</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348019</v>
+        <v>347966</v>
       </c>
       <c r="R3" t="n">
-        <v>6396625</v>
+        <v>6396622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B4" t="n">
-        <v>96380</v>
+        <v>80573</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R4" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B3" t="n">
-        <v>96380</v>
+        <v>80573</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R3" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710723</v>
+        <v>121710780</v>
       </c>
       <c r="B4" t="n">
-        <v>80573</v>
+        <v>96380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347973</v>
+        <v>347966</v>
       </c>
       <c r="R4" t="n">
-        <v>6396614</v>
+        <v>6396622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710606</v>
+        <v>121710780</v>
       </c>
       <c r="B2" t="n">
-        <v>80573</v>
+        <v>96398</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348019</v>
+        <v>347966</v>
       </c>
       <c r="R2" t="n">
-        <v>6396625</v>
+        <v>6396622</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>121710723</v>
       </c>
       <c r="B3" t="n">
-        <v>80573</v>
+        <v>80586</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710780</v>
+        <v>121710606</v>
       </c>
       <c r="B4" t="n">
-        <v>96380</v>
+        <v>80586</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347966</v>
+        <v>348019</v>
       </c>
       <c r="R4" t="n">
-        <v>6396622</v>
+        <v>6396625</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B2" t="n">
-        <v>96398</v>
+        <v>80588</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R2" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710723</v>
+        <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>80586</v>
+        <v>96666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347973</v>
+        <v>347966</v>
       </c>
       <c r="R3" t="n">
-        <v>6396614</v>
+        <v>6396622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>121710606</v>
       </c>
       <c r="B4" t="n">
-        <v>80586</v>
+        <v>80588</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121710723</v>
       </c>
       <c r="B2" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>96666</v>
+        <v>96673</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121710606</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121710723</v>
       </c>
       <c r="B2" t="n">
-        <v>80589</v>
+        <v>80596</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>96673</v>
+        <v>96682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>121710606</v>
       </c>
       <c r="B4" t="n">
-        <v>80589</v>
+        <v>80596</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710723</v>
+        <v>121710606</v>
       </c>
       <c r="B2" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347973</v>
+        <v>348019</v>
       </c>
       <c r="R2" t="n">
-        <v>6396614</v>
+        <v>6396625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,7 +780,7 @@
         <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>96682</v>
+        <v>96690</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710606</v>
+        <v>121710723</v>
       </c>
       <c r="B4" t="n">
-        <v>80596</v>
+        <v>80600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>348019</v>
+        <v>347973</v>
       </c>
       <c r="R4" t="n">
-        <v>6396625</v>
+        <v>6396614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710606</v>
+        <v>121710723</v>
       </c>
       <c r="B2" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>348019</v>
+        <v>347973</v>
       </c>
       <c r="R2" t="n">
-        <v>6396625</v>
+        <v>6396614</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710780</v>
+        <v>121710606</v>
       </c>
       <c r="B3" t="n">
-        <v>96690</v>
+        <v>80602</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>347966</v>
+        <v>348019</v>
       </c>
       <c r="R3" t="n">
-        <v>6396622</v>
+        <v>6396625</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710723</v>
+        <v>121710780</v>
       </c>
       <c r="B4" t="n">
-        <v>80600</v>
+        <v>96692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347973</v>
+        <v>347966</v>
       </c>
       <c r="R4" t="n">
-        <v>6396614</v>
+        <v>6396622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51542-2024 artfynd.xlsx
+++ b/artfynd/A 51542-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121710723</v>
+        <v>121710606</v>
       </c>
       <c r="B2" t="n">
         <v>80602</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>347973</v>
+        <v>348019</v>
       </c>
       <c r="R2" t="n">
-        <v>6396614</v>
+        <v>6396625</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121710606</v>
+        <v>121710780</v>
       </c>
       <c r="B3" t="n">
-        <v>80602</v>
+        <v>96692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1049</v>
+        <v>2569</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>348019</v>
+        <v>347966</v>
       </c>
       <c r="R3" t="n">
-        <v>6396625</v>
+        <v>6396622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121710780</v>
+        <v>121710723</v>
       </c>
       <c r="B4" t="n">
-        <v>96692</v>
+        <v>80602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2569</v>
+        <v>1049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>347966</v>
+        <v>347973</v>
       </c>
       <c r="R4" t="n">
-        <v>6396622</v>
+        <v>6396614</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
